--- a/docs/data/skills.xlsx
+++ b/docs/data/skills.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rf3bf160aaae449b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta" sheetId="2" r:id="R924f7f1313c74872"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="3" r:id="R33af6c0ea0214785"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TeachStock" sheetId="4" r:id="Re0088c117b4d4c80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R13e1da2c62474db4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta" sheetId="2" r:id="Rc5eabedde7084f55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="3" r:id="R895c1162be90473f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TeachStock" sheetId="4" r:id="Rfabc75df45c2489f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1134,7 +1134,7 @@
         <x:v>NG神教架构高级功法，以依赖注入调度周身，护身养气、适合冥想。</x:v>
       </x:c>
       <x:c r="AB9" s="26" t="str">
-        <x:v>{"ult":{"key":"ng","kind":"multi","names":["依赖注入·定海","AOT·万法归一"]}}</x:v>
+        <x:v>{"ult":{"key":"ng","abilitySets":[["multi"],["multi"]],"mpCosts":[25,45],"names":["依赖注入·定海","AOT·万法归一"]}}</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1370,7 +1370,7 @@
         <x:v>香草派架构高级功法，封存内劲，适合冥想养气。</x:v>
       </x:c>
       <x:c r="AB13" s="26" t="str">
-        <x:v>{"ult":{"key":"vanilla","kind":"abnormal","names":["闭包·封天","原生·归真一击"]}}</x:v>
+        <x:v>{"ult":{"key":"vanilla","abilitySets":[["abnormal"],["abnormal"]],"mpCosts":[30,50],"names":["闭包·封天","原生·归真一击"]}}</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1608,7 +1608,7 @@
         <x:v>量子仙宗架构高级功法，归一状态，适合冥想养气。</x:v>
       </x:c>
       <x:c r="AB17" s="26" t="str">
-        <x:v>{"ult":{"key":"react","kind":"reduceMax","names":["钩式·千手","并发·量子千幻"]}}</x:v>
+        <x:v>{"ult":{"key":"react","abilitySets":[["drain_hp"],["drain_mp"]],"mpCosts":[35,60],"names":["钩式·千手","并发·量子千幻"]}}</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1846,7 +1846,7 @@
         <x:v>鱿鱼山庄架构高级功法，响应周身气机，适合冥想养气。</x:v>
       </x:c>
       <x:c r="AB21" s="26" t="str">
-        <x:v>{"ult":{"key":"vue","kind":"hugeDamage","names":["响应·千丝","Vite·瞬息万变"]}}</x:v>
+        <x:v>{"ult":{"key":"vue","abilitySets":[["guaranteed_hit"],["guaranteed_hit"]],"mpCosts":[40,70],"names":["响应·千丝","Vite·瞬息万变"]}}</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
